--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -462,42 +462,42 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>479</v>
+        <v>1677</v>
       </c>
       <c r="C3" t="n">
-        <v>150</v>
+        <v>1322</v>
       </c>
       <c r="D3" t="n">
-        <v>329</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Girls</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>118</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Girls</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,188 +564,188 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>373658</v>
+        <v>373696</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373712</v>
+        <v>373642</v>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alia Khan</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373681</v>
+        <v>373646</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373692</v>
+        <v>373648</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Asma Bibi</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373710</v>
+        <v>373641</v>
       </c>
       <c r="C7" t="n">
+        <v>106</v>
+      </c>
+      <c r="D7" t="n">
+        <v>85</v>
+      </c>
+      <c r="E7" t="n">
         <v>21</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373691</v>
+        <v>373684</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>178</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Naureen</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>884887</v>
+        <v>373649</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sajjad Khan</t>
+          <t>Muhammad Yousaf</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373700</v>
+        <v>373690</v>
       </c>
       <c r="C10" t="n">
+        <v>72</v>
+      </c>
+      <c r="D10" t="n">
+        <v>64</v>
+      </c>
+      <c r="E10" t="n">
         <v>8</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Muhammad naeem</t>
+          <t>Jaweria</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>571571</v>
+        <v>163495</v>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Zain Ul Abideen</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373667</v>
+        <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -754,93 +754,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373646</v>
+        <v>373705</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
+        <v>47</v>
+      </c>
+      <c r="E13" t="n">
         <v>4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Furqan Ullah Khan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373651</v>
+        <v>373683</v>
       </c>
       <c r="C14" t="n">
+        <v>55</v>
+      </c>
+      <c r="D14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E14" t="n">
         <v>9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hijab Zahra</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373637</v>
+        <v>373671</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Muniba Shamim</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373659</v>
+        <v>373673</v>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Furqan Ullah Khan</t>
+          <t>Asma Gull</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>373683</v>
+        <v>373672</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="E17" t="n">
         <v>8</v>
@@ -849,302 +849,302 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Asma Gull</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>373672</v>
+        <v>373706</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bushra Ayub</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>373671</v>
+        <v>373651</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Syed Haider Abbas</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>373713</v>
+        <v>373665</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373696</v>
+        <v>373710</v>
       </c>
       <c r="C21" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Naureen</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>373706</v>
+        <v>884887</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Laiba Khan</t>
+          <t>Muniba Shamim</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>373653</v>
+        <v>373659</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mahnoorr</t>
+          <t>Munawar Khan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>373670</v>
+        <v>373668</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Samreen</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>639258</v>
+        <v>564273</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Lati khan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>373684</v>
+        <v>671211</v>
       </c>
       <c r="C26" t="n">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E26" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>373648</v>
+        <v>453925</v>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Asma Bibi</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>373641</v>
+        <v>373712</v>
       </c>
       <c r="C28" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>373649</v>
+        <v>373692</v>
       </c>
       <c r="C29" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Chashm Gul</t>
+          <t>Anum Gul</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>373695</v>
+        <v>373656</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>373642</v>
+        <v>373658</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Muhammad Yousaf</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>373690</v>
+        <v>373691</v>
       </c>
       <c r="C32" t="n">
+        <v>34</v>
+      </c>
+      <c r="D32" t="n">
         <v>7</v>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Anum Gul</t>
+          <t>Alia Khan</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>373656</v>
+        <v>373681</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
         <v>5</v>
@@ -1153,36 +1153,36 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Khalida Bibi</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>373673</v>
+        <v>373699</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Laiba Khan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>373705</v>
+        <v>373653</v>
       </c>
       <c r="C35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" t="n">
         <v>4</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
@@ -1191,190 +1191,266 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Nazia</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>373699</v>
+        <v>373657</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Nillum Bibi</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>373665</v>
+        <v>373652</v>
       </c>
       <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="n">
         <v>3</v>
       </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Muhammad Naeem</t>
+          <t>Zain Ul Abideen</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>373694</v>
+        <v>373667</v>
       </c>
       <c r="C38" t="n">
         <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nillum Bibi</t>
+          <t>Muhammad Noor</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>373652</v>
+        <v>373701</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Munawar Khan</t>
+          <t>Muhammad Shahid Khan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>373668</v>
+        <v>373662</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Shehla Noor</t>
+          <t>Chashm Gul</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>373650</v>
+        <v>373695</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jaweria</t>
+          <t>Muhammad naeem</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>163495</v>
+        <v>571571</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Muhammad Naeem</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>564273</v>
+        <v>373694</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Muhammad Noor</t>
+          <t>Shehla Noor</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>373701</v>
+        <v>373650</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>Aisha Aman</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>373704</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Mahnoorr</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>373670</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Rahila Naaz</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>373715</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Robina Shaheen</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>373639</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>Sidra Khan</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B49" t="n">
         <v>373645</v>
       </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1020,96 +1020,96 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>453925</v>
+        <v>373658</v>
       </c>
       <c r="C27" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="D27" t="n">
         <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>373712</v>
+        <v>453925</v>
       </c>
       <c r="C28" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D28" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>373692</v>
+        <v>373712</v>
       </c>
       <c r="C29" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Anum Gul</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>373656</v>
+        <v>373692</v>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D30" t="n">
         <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Anum Gul</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>373658</v>
+        <v>373656</v>
       </c>
       <c r="C31" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1122,13 +1122,13 @@
         <v>373691</v>
       </c>
       <c r="C32" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -446,10 +446,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2102</v>
+        <v>2250</v>
       </c>
       <c r="C2" t="n">
-        <v>2102</v>
+        <v>2250</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -462,13 +462,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1677</v>
+        <v>1656</v>
       </c>
       <c r="C3" t="n">
-        <v>1322</v>
+        <v>1448</v>
       </c>
       <c r="D3" t="n">
-        <v>355</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4">
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>97</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,10 +552,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2102</v>
+        <v>2250</v>
       </c>
       <c r="D2" t="n">
-        <v>2102</v>
+        <v>2250</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -571,51 +571,51 @@
         <v>373696</v>
       </c>
       <c r="C3" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373642</v>
+        <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D4" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373646</v>
+        <v>373642</v>
       </c>
       <c r="C5" t="n">
+        <v>108</v>
+      </c>
+      <c r="D5" t="n">
         <v>104</v>
       </c>
-      <c r="D5" t="n">
-        <v>96</v>
-      </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -628,13 +628,13 @@
         <v>373648</v>
       </c>
       <c r="C6" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D6" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -647,51 +647,51 @@
         <v>373641</v>
       </c>
       <c r="C7" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D7" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373684</v>
+        <v>373649</v>
       </c>
       <c r="C8" t="n">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="D8" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E8" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373649</v>
+        <v>373684</v>
       </c>
       <c r="C9" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -704,10 +704,10 @@
         <v>373690</v>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D10" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E10" t="n">
         <v>8</v>
@@ -723,10 +723,10 @@
         <v>163495</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -742,10 +742,10 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -754,131 +754,131 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373705</v>
+        <v>373651</v>
       </c>
       <c r="C13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D13" t="n">
         <v>51</v>
       </c>
-      <c r="D13" t="n">
-        <v>47</v>
-      </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Furqan Ullah Khan</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373683</v>
+        <v>373705</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bushra Ayub</t>
+          <t>Furqan Ullah Khan</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373671</v>
+        <v>373683</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Khalida Bibi</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373673</v>
+        <v>373671</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Asma Gull</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>373672</v>
+        <v>373673</v>
       </c>
       <c r="C17" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Asma Gull</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>373706</v>
+        <v>373672</v>
       </c>
       <c r="C18" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>373651</v>
+        <v>373706</v>
       </c>
       <c r="C19" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
@@ -894,162 +894,162 @@
         <v>373665</v>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Naureen</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373710</v>
+        <v>884887</v>
       </c>
       <c r="C21" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D21" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Naureen</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>884887</v>
+        <v>564273</v>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" t="n">
         <v>28</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Muniba Shamim</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>373659</v>
+        <v>373710</v>
       </c>
       <c r="C23" t="n">
         <v>40</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Munawar Khan</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>373668</v>
+        <v>453925</v>
       </c>
       <c r="C24" t="n">
         <v>25</v>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Muniba Shamim</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>564273</v>
+        <v>373659</v>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lati khan</t>
+          <t>Munawar Khan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>671211</v>
+        <v>373668</v>
       </c>
       <c r="C26" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>373658</v>
+        <v>373692</v>
       </c>
       <c r="C27" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Lati khan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>453925</v>
+        <v>671211</v>
       </c>
       <c r="C28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1065,10 +1065,10 @@
         <v>373712</v>
       </c>
       <c r="C29" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E29" t="n">
         <v>36</v>
@@ -1077,20 +1077,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>373692</v>
+        <v>373658</v>
       </c>
       <c r="C30" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E30" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
@@ -1106,10 +1106,10 @@
         <v>17</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1122,13 +1122,13 @@
         <v>373691</v>
       </c>
       <c r="C32" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E32" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
@@ -1141,29 +1141,29 @@
         <v>373681</v>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Irum ikram</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>373699</v>
+        <v>541376</v>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
@@ -1172,96 +1172,96 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Laiba Khan</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>373653</v>
+        <v>373699</v>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nazia</t>
+          <t>Laiba Khan</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>373657</v>
+        <v>373653</v>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D36" t="n">
         <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nillum Bibi</t>
+          <t>Nazia</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>373652</v>
+        <v>373657</v>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Zain Ul Abideen</t>
+          <t>Nillum Bibi</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>373667</v>
+        <v>373652</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
         <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Muhammad Noor</t>
+          <t>Zain Ul Abideen</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>373701</v>
+        <v>373667</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1274,10 +1274,10 @@
         <v>373662</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1312,61 +1312,61 @@
         <v>571571</v>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Muhammad Naeem</t>
+          <t>Aisha Aman</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>373694</v>
+        <v>373704</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Shehla Noor</t>
+          <t>Mahnoorr</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>373650</v>
+        <v>373670</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Aisha Aman</t>
+          <t>Muhammad Noor</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>373704</v>
+        <v>373701</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1381,11 +1381,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mahnoorr</t>
+          <t>Rahila Naaz</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>373670</v>
+        <v>373715</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1400,11 +1400,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Rahila Naaz</t>
+          <t>Robina Shaheen</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>373715</v>
+        <v>373639</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1413,44 +1413,6 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Robina Shaheen</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>373639</v>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Sidra Khan</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>373645</v>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,26 +426,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -446,13 +458,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2250</v>
+        <v>2437</v>
       </c>
       <c r="C2" t="n">
-        <v>2250</v>
+        <v>2435</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -462,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1656</v>
+        <v>1924</v>
       </c>
       <c r="C3" t="n">
-        <v>1448</v>
+        <v>1673</v>
       </c>
       <c r="D3" t="n">
-        <v>208</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4">
@@ -478,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>172</v>
+        <v>608</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>252</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5">
@@ -494,13 +506,29 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Household vs Girls</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -514,31 +542,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -552,295 +580,295 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2250</v>
+        <v>2437</v>
       </c>
       <c r="D2" t="n">
-        <v>2250</v>
+        <v>2435</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>373696</v>
+        <v>373646</v>
       </c>
       <c r="C3" t="n">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="D3" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373646</v>
+        <v>373696</v>
       </c>
       <c r="C4" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D4" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373642</v>
+        <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="D5" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Asma Bibi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373648</v>
+        <v>373641</v>
       </c>
       <c r="C6" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D6" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Asma Bibi</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373641</v>
+        <v>373642</v>
       </c>
       <c r="C7" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373649</v>
+        <v>373684</v>
       </c>
       <c r="C8" t="n">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373684</v>
+        <v>373649</v>
       </c>
       <c r="C9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Muhammad Yousaf</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373690</v>
+        <v>373692</v>
       </c>
       <c r="C10" t="n">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jaweria</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>163495</v>
+        <v>373658</v>
       </c>
       <c r="C11" t="n">
-        <v>56</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373716</v>
+        <v>373691</v>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>174</v>
       </c>
       <c r="D12" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Furqan Ullah Khan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373651</v>
+        <v>373683</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373705</v>
+        <v>373673</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Furqan Ullah Khan</t>
+          <t>Muhammad Yousaf</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373683</v>
+        <v>373690</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bushra Ayub</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373671</v>
+        <v>373651</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Khalida Bibi</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>373673</v>
+        <v>373716</v>
       </c>
       <c r="C17" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -849,17 +877,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Asma Gull</t>
+          <t>Jaweria</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>373672</v>
+        <v>163495</v>
       </c>
       <c r="C18" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -868,55 +896,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>373706</v>
+        <v>373671</v>
       </c>
       <c r="C19" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>373665</v>
+        <v>373705</v>
       </c>
       <c r="C20" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Naureen</t>
+          <t>Asma Gull</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>884887</v>
+        <v>373672</v>
       </c>
       <c r="C21" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
@@ -925,93 +953,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>564273</v>
+        <v>453925</v>
       </c>
       <c r="C22" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D22" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>373710</v>
+        <v>373712</v>
       </c>
       <c r="C23" t="n">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c r="D23" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E23" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>453925</v>
+        <v>564273</v>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Muniba Shamim</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>373659</v>
+        <v>373665</v>
       </c>
       <c r="C25" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D25" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Munawar Khan</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>373668</v>
+        <v>373706</v>
       </c>
       <c r="C26" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E26" t="n">
         <v>6</v>
@@ -1020,131 +1048,131 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Irum ikram</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>373692</v>
+        <v>541376</v>
       </c>
       <c r="C27" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E27" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lati khan</t>
+          <t>Naureen</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>671211</v>
+        <v>884887</v>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>373712</v>
+        <v>373710</v>
       </c>
       <c r="C29" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E29" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Muniba Shamim</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>373658</v>
+        <v>373659</v>
       </c>
       <c r="C30" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E30" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Anum Gul</t>
+          <t>Munawar Khan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>373656</v>
+        <v>373668</v>
       </c>
       <c r="C31" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Lati khan</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>373691</v>
+        <v>671211</v>
       </c>
       <c r="C32" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E32" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alia Khan</t>
+          <t>Anum Gul</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>373681</v>
+        <v>373656</v>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E33" t="n">
         <v>4</v>
@@ -1153,74 +1181,74 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Irum ikram</t>
+          <t>Alia Khan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>541376</v>
+        <v>373681</v>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Nillum Bibi</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>373699</v>
+        <v>373652</v>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Laiba Khan</t>
+          <t>Nazia</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>373653</v>
+        <v>373657</v>
       </c>
       <c r="C36" t="n">
         <v>8</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nazia</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>373657</v>
+        <v>373699</v>
       </c>
       <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
-      </c>
-      <c r="D37" t="n">
-        <v>4</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1229,30 +1257,30 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nillum Bibi</t>
+          <t>Laiba Khan</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>373652</v>
+        <v>373653</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Zain Ul Abideen</t>
+          <t>Shehla Noor</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>373667</v>
+        <v>373650</v>
       </c>
       <c r="C39" t="n">
         <v>3</v>
@@ -1267,17 +1295,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Muhammad Shahid Khan</t>
+          <t>Zain Ul Abideen</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>373662</v>
+        <v>373667</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1286,68 +1314,68 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Chashm Gul</t>
+          <t>Muhammad Shahid Khan</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>373695</v>
+        <v>373662</v>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
         <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Muhammad naeem</t>
+          <t>Chashm Gul</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>571571</v>
+        <v>373695</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Aisha Aman</t>
+          <t>Muhammad naeem</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>373704</v>
+        <v>571571</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mahnoorr</t>
+          <t>Aisha Aman</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>373670</v>
+        <v>373704</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -1362,11 +1390,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Muhammad Noor</t>
+          <t>Mahnoorr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>373701</v>
+        <v>373670</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1381,11 +1409,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Rahila Naaz</t>
+          <t>Muhammad Noor</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>373715</v>
+        <v>373701</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1400,11 +1428,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Robina Shaheen</t>
+          <t>Rahila Naaz</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>373639</v>
+        <v>373715</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1413,6 +1441,25 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Robina Shaheen</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>373639</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
         <v>1</v>
       </c>
     </row>
